--- a/docs/qa/upload-templates/purchase_orders_upload_template.xlsx
+++ b/docs/qa/upload-templates/purchase_orders_upload_template.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,22 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>currency</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>expected_delivery</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>warehouse</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>status</t>
         </is>
       </c>
     </row>
@@ -488,7 +503,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>WH-RM</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -516,7 +546,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>WH-RM</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>confirmed</t>
         </is>
       </c>
     </row>
@@ -533,7 +578,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>RM-CORE</t>
+          <t>SF-CORE100</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -544,7 +589,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>EGP</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>WH-WIP</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>draft</t>
         </is>
       </c>
     </row>
